--- a/product/candle-calculator/dist/tests/T5a.xlsx
+++ b/product/candle-calculator/dist/tests/T5a.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Your Candle" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Costs &amp; Price" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Reference" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Candle" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Costs &amp; Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -36,17 +34,16 @@
     <font>
       <b val="1"/>
       <color rgb="00263238"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00546E7A"/>
-      <sz val="9"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="0078909C"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -58,12 +55,12 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00C62828"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -75,22 +72,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00263238"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F3F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,34 +123,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,149 +514,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Candle Batch &amp; Pricing Calculator</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Work out exactly how much wax and fragrance to melt, what each candle costs you, and what to charge.</t>
+          <t>Candle</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Weigh in</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>grams</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>First, two quick settings</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>I weigh things in</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>grams</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Everything below switches to match.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>$</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Currency symbol</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Just for labels. Nothing is converted.</t>
-        </is>
-      </c>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Short unit label</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>IF($B$5="grams","g","oz")</f>
-        <v/>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>These two lines do the unit switching. Leave them as they are.</t>
+          <t>Water weight</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C7">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>jar filled to your line</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Grams in one of your units</t>
-        </is>
-      </c>
-      <c r="B8" s="7">
-        <f>IF($B$5="grams",1,28.349523125)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>The one thing that trips people up</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+          <t>Wax factor</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>planning assumption — waxes vary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fill weight</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <f>IF(OR($B$7="",$B$8=""),"",$B$7*$B$8)</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Fragrance load and fragrance content are different numbers.</t>
-        </is>
-      </c>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fragrance</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fragrance LOAD is a percentage of the wax on its own.</t>
+          <t>Measured as</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Load (% of wax)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>load = % of wax · content = % of wax + fragrance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fragrance CONTENT is a percentage of the wax and fragrance added together.</t>
-        </is>
+          <t>Fragrance %</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Put 20 g of fragrance into 200 g of wax and you have a 10% load — but 9.09% content (20 out of 220 g).</t>
+          <t>Wax maximum</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>optional — from your wax spec sheet</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Same candle. Two numbers. Use whichever your recipe or your wax sheet uses — this sheet always shows you both.</t>
-        </is>
+      <c r="B15" s="10">
+        <f>IF(OR($B$9="",$B$13="",$B$13&gt;=1),"",IF(AND($B$14&lt;&gt;"",$B$13&gt;$B$14),"Above the maximum you entered ("&amp;TEXT($B$14,"0.0%")&amp;"). Your wax may not hold it.",""))</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>How to measure your jar</t>
+          <t>Per candle</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -671,62 +682,155 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1. Put your empty jar on the scale and zero it.</t>
-        </is>
+          <t>Wax</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>IF(OR($B$9="",$B$13="",$B$13&gt;=1),"",IF($B$12="Load (% of wax)",$B$9/(1+$B$13),$B$9*(1-$B$13)))</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2. Fill it with water to the height you want the wax to reach, leaving room for the lid.</t>
-        </is>
+          <t>Fragrance oil</t>
+        </is>
+      </c>
+      <c r="B19" s="11">
+        <f>IF(OR($B$9="",$B$13="",$B$13&gt;=1),"",IF($B$12="Load (% of wax)",$B$9*$B$13/(1+$B$13),$B$9*$B$13))</f>
+        <v/>
+      </c>
+      <c r="C19">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3. Write that water weight down. That is the number this sheet starts from.</t>
+          <t>Fill weight</t>
+        </is>
+      </c>
+      <c r="B20" s="12">
+        <f>IF($B$9="","",$B$9)</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>IF(OR($B$9="",$B$13="",$B$13&gt;=1),"",IF($B$12="Load (% of wax)",$B$13,$B$13/(1-$B$13)))</f>
+        <v/>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>% of wax</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Colour key</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Type in these</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>IF(OR($B$9="",$B$13="",$B$13&gt;=1),"",IF($B$12="Load (% of wax)",$B$13/(1+$B$13),$B$13))</f>
+        <v/>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>% of wax + fragrance</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>These work themselves out — don't type over them</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Batch</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Starting assumptions you can change</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n"/>
+          <t>Candles</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pitcher loss</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>extra wax left in the pitcher</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Wax</t>
+        </is>
+      </c>
+      <c r="B27" s="11">
+        <f>IF(OR($B$18="",$B$25=""),"",$B$18*$B$25*(1+$B$26))</f>
+        <v/>
+      </c>
+      <c r="C27">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Fragrance oil</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>IF(OR($B$19="",$B$25=""),"",$B$19*$B$25*(1+$B$26))</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>IF('Candle'!$B$3="grams","g","oz")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <mergeCells count="1">
+    <mergeCell ref="B15:D15"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"grams,ounces"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Load (% of wax),Content (% of wax + fragrance)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -739,26 +843,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Your Candle</t>
+          <t>Costs &amp; Price</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Your jar</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -766,345 +870,53 @@
       <c r="D3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Water weight of your jar, filled to your line</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="n">
-        <v>300</v>
-      </c>
-      <c r="C4">
-        <f>'Start Here'!$B$7</f>
-        <v/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Price paid</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Water-to-wax factor</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>0.86</v>
+          <t>Wax</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>A planning assumption, not a physical constant. Waxes differ — measure your own and change this.</t>
+          <t>kg</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fill weight — how much wax + fragrance fits</t>
-        </is>
-      </c>
-      <c r="B6" s="13">
-        <f>IF(OR($B$4="",$B$5=""),"",$B$4*$B$5)</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>'Start Here'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Your fragrance</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>How you measure fragrance</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Fragrance load (% of wax)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>This sheet shows you both numbers either way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fragrance percentage</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Maximum your wax can hold</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Optional. From your wax's spec sheet — enter it the same way you are measuring above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="15">
-        <f>IF(OR($B$6="",$B$10="",$B$10&gt;=1),"",IF(AND($B$11&lt;&gt;"",$B$10&gt;$B$11),"Above the maximum you entered for this wax ("&amp;TEXT($B$11,"0.0%")&amp;"). Your wax may not hold it.",""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>One candle</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Wax</t>
-        </is>
-      </c>
-      <c r="B15" s="16">
-        <f>IF(OR($B$6="",$B$10="",$B$10&gt;=1),"",IF($B$9="Fragrance load (% of wax)",$B$6/(1+$B$10),$B$6*(1-$B$10)))</f>
-        <v/>
-      </c>
-      <c r="C15">
-        <f>'Start Here'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>Fragrance oil</t>
         </is>
       </c>
-      <c r="B16" s="16">
-        <f>IF(OR($B$6="",$B$10="",$B$10&gt;=1),"",IF($B$9="Fragrance load (% of wax)",$B$6*$B$10/(1+$B$10),$B$6*$B$10))</f>
-        <v/>
-      </c>
-      <c r="C16">
-        <f>'Start Here'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total fill weight</t>
-        </is>
-      </c>
-      <c r="B17" s="17">
-        <f>IF($B$6="","",$B$6)</f>
-        <v/>
-      </c>
-      <c r="C17">
-        <f>'Start Here'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Fragrance load (% of wax)</t>
-        </is>
-      </c>
-      <c r="B18" s="18">
-        <f>IF(OR($B$6="",$B$10="",$B$10&gt;=1),"",IF($B$9="Fragrance load (% of wax)",$B$10,$B$10/(1-$B$10)))</f>
-        <v/>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Both are shown on purpose. They describe the same candle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fragrance content (% of wax + fragrance)</t>
-        </is>
-      </c>
-      <c r="B19" s="18">
-        <f>IF(OR($B$6="",$B$10="",$B$10&gt;=1),"",IF($B$9="Fragrance load (% of wax)",$B$10/(1+$B$10),$B$10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Your batch</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>How many candles in this batch</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Extra wax for what stays in the pitcher</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Starts at 0%. Raise it if you know how much you normally lose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Wax for the whole batch</t>
-        </is>
-      </c>
-      <c r="B24" s="16">
-        <f>IF(OR($B$15="",$B$22=""),"",$B$15*$B$22*(1+$B$23))</f>
-        <v/>
-      </c>
-      <c r="C24">
-        <f>'Start Here'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Fragrance oil for the whole batch</t>
-        </is>
-      </c>
-      <c r="B25" s="16">
-        <f>IF(OR($B$16="",$B$22=""),"",$B$16*$B$22*(1+$B$23))</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>'Start Here'!$B$7</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B12:D12"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Fragrance load (% of wax),Fragrance content (% of wax + fragrance)"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Costs &amp; Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>What your materials cost</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>What you paid</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>How much that bought</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Sold in</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Wax</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Fragrance oil</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>g</t>
         </is>
@@ -1113,29 +925,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cost of wax, per unit you weigh in</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
-        <f>IF(OR($B$5="",$C$5="",$C$5=0),"",$B$5/($C$5*IF($D$5="g",1,IF($D$5="kg",1000,IF($D$5="oz",28.349523125,453.59237)))/'Start Here'!$B$8))</f>
+          <t>Wax per unit</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>IF(OR($B$5="",$C$5="",$C$5=0),"",$B$5/($C$5*IF($D$5="g",1,IF($D$5="kg",1000,IF($D$5="oz",28.349523125,453.59237)))/IF('Candle'!$B$3="grams",1,28.349523125)))</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cost of fragrance oil, per unit you weigh in</t>
-        </is>
-      </c>
-      <c r="B8" s="22">
-        <f>IF(OR($B$6="",$C$6="",$C$6=0),"",$B$6/($C$6*IF($D$6="g",1,IF($D$6="kg",1000,IF($D$6="oz",28.349523125,453.59237)))/'Start Here'!$B$8))</f>
+          <t>Fragrance per unit</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>IF(OR($B$6="",$C$6="",$C$6=0),"",$B$6/($C$6*IF($D$6="g",1,IF($D$6="kg",1000,IF($D$6="oz",28.349523125,453.59237)))/IF('Candle'!$B$3="grams",1,28.349523125)))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Parts for one candle</t>
+          <t>Parts per candle</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -1148,7 +960,7 @@
           <t>Vessel</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="17" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -1158,7 +970,7 @@
           <t>Wick</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -1168,7 +980,7 @@
           <t>Lid</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="17" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1178,34 +990,34 @@
           <t>Label</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="17" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Box or packaging</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="n">
+          <t>Packaging</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
         <v>0.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Anything else</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="n">
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Your time (optional)</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1215,40 +1027,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Pay myself for my time</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Your time is a real cost. If you skip this, your price only covers materials.</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>optional</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Minutes to make one candle</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n"/>
+          <t>Minutes per candle</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>What I pay myself per hour</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="n"/>
+          <t>Hourly rate</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Your running costs (optional)</t>
+          <t>Overhead</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1258,46 +1070,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Include my monthly running costs</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Rent, insurance, subscriptions — costs you pay whether or not you make a candle this month.</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>optional — rent, insurance, subscriptions</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>My monthly running costs</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="n"/>
+          <t>Monthly cost</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Candles I make in a month</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n"/>
+          <t>Candles per month</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="15">
-        <f>IF(AND($B$24="Yes",OR($B$26="",$B$26=0)),"Enter how many candles you make in a month, or switch running costs off.","")</f>
+      <c r="B27" s="10">
+        <f>IF(AND($B$24="Yes",OR($B$26="",$B$26=0)),"Enter candles per month, or set Include to No.","")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>What one candle costs you</t>
+          <t>Cost per candle</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1310,18 +1122,18 @@
           <t>Wax + fragrance</t>
         </is>
       </c>
-      <c r="B30" s="23">
-        <f>IF(OR('Your Candle'!$B$24="",$B$7="",$B$8="",'Your Candle'!$B$22=""),"",('Your Candle'!$B$24*$B$7+'Your Candle'!$B$25*$B$8)/'Your Candle'!$B$22)</f>
+      <c r="B30" s="19">
+        <f>IF(OR('Candle'!$B$27="",$B$7="",$B$8="",'Candle'!$B$25=""),"",('Candle'!$B$27*$B$7+'Candle'!$B$28*$B$8)/'Candle'!$B$25)</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Other parts</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="B31" s="19">
         <f>SUM($B$11:$B$16)</f>
         <v/>
       </c>
@@ -1329,10 +1141,10 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Your time</t>
-        </is>
-      </c>
-      <c r="B32" s="23">
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="B32" s="19">
         <f>IF($B$19&lt;&gt;"Yes",0,IF(OR($B$20="",$B$21=""),"",$B$20/60*$B$21))</f>
         <v/>
       </c>
@@ -1340,10 +1152,10 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Share of running costs</t>
-        </is>
-      </c>
-      <c r="B33" s="23">
+          <t>Overhead</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
         <f>IF($B$24&lt;&gt;"Yes",0,IF(OR($B$25="",$B$26="",$B$26=0),"",$B$25/$B$26))</f>
         <v/>
       </c>
@@ -1351,10 +1163,10 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TOTAL cost per candle</t>
-        </is>
-      </c>
-      <c r="B34" s="24">
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B34" s="20">
         <f>IF(OR($B$30="",$B$32="",$B$33=""),"",$B$30+$B$31+$B$32+$B$33)</f>
         <v/>
       </c>
@@ -1362,7 +1174,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Where you're selling</t>
+          <t>Selling fees</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1372,84 +1184,89 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Where am I selling this</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Fees change. Look up your marketplace's current fees and type them in — this sheet does not guess them for you.</t>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>look up your marketplace's current fees</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Selling fee %</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="n"/>
+          <t>Selling fee</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Payment processing %</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="n"/>
+          <t>Processing</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Any other % fee</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="n"/>
+          <t>Other %</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fixed fee per order</t>
-        </is>
-      </c>
-      <c r="B41" s="21" t="n"/>
+          <t>Fixed per order</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Percentage fees apply to</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Item price only</t>
+          <t>Charged on</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Item only</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>item only, or item + shipping</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Shipping I charge the buyer</t>
-        </is>
-      </c>
-      <c r="B43" s="21" t="n">
+          <t>Shipping charged</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>What shipping actually costs me</t>
-        </is>
-      </c>
-      <c r="B44" s="21" t="n">
+          <t>Shipping cost</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Your price</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -1459,53 +1276,53 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Profit margin I want</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="n">
+          <t>Target margin</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>As a share of the price you charge.</t>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>share of price, not markup on cost</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Price to charge</t>
-        </is>
-      </c>
-      <c r="B48" s="24">
-        <f>IF(OR($B$34="",$B$47=""),"",IF((1-SUM($B$38:$B$40)-$B$47)&lt;=0,"",(IF($B$41="",0,$B$41)+$B$34+IF($B$44="",0,$B$44)-IF($B$42="Item price + shipping",IF($B$43="",0,$B$43)*(1-SUM($B$38:$B$40)),IF($B$43="",0,$B$43)))/(1-SUM($B$38:$B$40)-$B$47)))</f>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B48" s="20">
+        <f>IF(OR($B$34="",$B$47=""),"",IF((1-SUM($B$38:$B$40)-$B$47)&lt;=0,"",(IF($B$41="",0,$B$41)+$B$34+IF($B$44="",0,$B$44)-IF($B$42="Item + shipping",IF($B$43="",0,$B$43)*(1-SUM($B$38:$B$40)),IF($B$43="",0,$B$43)))/(1-SUM($B$38:$B$40)-$B$47)))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="15">
-        <f>IF(OR($B$34="",$B$47=""),"",IF((1-SUM($B$38:$B$40)-$B$47)&lt;=0,"A "&amp;TEXT($B$47,"0%")&amp;" margin isn't reachable with fees of "&amp;TEXT(SUM($B$38:$B$40),"0.0%")&amp;". Lower the margin or the fees — there is no price that works.",IF($B$48&lt;=0,"Check your shipping and fee figures — this comes out at or below zero.","")))</f>
+      <c r="B49" s="10">
+        <f>IF(OR($B$34="",$B$47=""),"",IF((1-SUM($B$38:$B$40)-$B$47)&lt;=0,"A "&amp;TEXT($B$47,"0%")&amp;" margin is not reachable with fees of "&amp;TEXT(SUM($B$38:$B$40),"0.0%")&amp;". Lower the margin or the fees.",IF($B$48&lt;=0,"Check the shipping and fee figures — this comes out at or below zero.","")))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fees on that sale</t>
-        </is>
-      </c>
-      <c r="B50" s="23">
-        <f>IF($B$48="","",SUM($B$38:$B$40)*IF($B$42="Item price + shipping",$B$48+IF($B$43="",0,$B$43),$B$48)+IF($B$41="",0,$B$41))</f>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="B50" s="19">
+        <f>IF($B$48="","",SUM($B$38:$B$40)*IF($B$42="Item + shipping",$B$48+IF($B$43="",0,$B$43),$B$48)+IF($B$41="",0,$B$41))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>You receive</t>
-        </is>
-      </c>
-      <c r="B51" s="23">
+          <t>Net received</t>
+        </is>
+      </c>
+      <c r="B51" s="19">
         <f>IF($B$48="","",$B$48+IF($B$43="",0,$B$43)-$B$50)</f>
         <v/>
       </c>
@@ -1513,10 +1330,10 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Your profit</t>
-        </is>
-      </c>
-      <c r="B52" s="25">
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="B52" s="21">
         <f>IF($B$48="","",$B$51-$B$34-IF($B$44="",0,$B$44))</f>
         <v/>
       </c>
@@ -1524,28 +1341,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Margin you actually get</t>
-        </is>
-      </c>
-      <c r="B53" s="18">
+          <t>Margin achieved</t>
+        </is>
+      </c>
+      <c r="B53" s="13">
         <f>IF(OR($B$48="",$B$48=0),"",$B$52/$B$48)</f>
         <v/>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Margin is profit as a share of your price. Markup is profit as a share of your cost. They are not the same number.</t>
-        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Markup on your cost</t>
-        </is>
-      </c>
-      <c r="B54" s="18">
+          <t>Markup</t>
+        </is>
+      </c>
+      <c r="B54" s="13">
         <f>IF(OR($B$34="",$B$34=0,$B$48=""),"",$B$52/$B$34)</f>
         <v/>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>profit ÷ cost</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1561,15 +1378,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Wholesale multiplier</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="n">
+          <t>Multiplier</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>A common starting point is 2 — twice what the candle costs you.</t>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>2 = twice your cost</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1396,7 @@
           <t>Wholesale price</t>
         </is>
       </c>
-      <c r="B58" s="24">
+      <c r="B58" s="20">
         <f>IF(OR($B$34="",$B$57=""),"",$B$34*$B$57)</f>
         <v/>
       </c>
@@ -1587,17 +1404,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A shop reselling at twice that would charge</t>
-        </is>
-      </c>
-      <c r="B59" s="23">
+          <t>Shop retail at 2x</t>
+        </is>
+      </c>
+      <c r="B59" s="19">
         <f>IF($B$58="","",$B$58*2)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="15">
-        <f>IF($B$58="","",IF($B$58&lt;$B$34,"This wholesale price is below what the candle costs you.",""))</f>
+      <c r="B60" s="10">
+        <f>IF($B$58="","",IF($B$58&lt;$B$34,"Wholesale price is below your cost per candle.",""))</f>
         <v/>
       </c>
     </row>
@@ -1621,25 +1438,25 @@
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Item price only,Item price + shipping"</formula1>
+      <formula1>"Item only,Item + shipping"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1652,312 +1469,348 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>What this sheet does not do</t>
+          <t>Wick sizing</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
-        <is>
-          <t>This workbook does not choose your wick.</t>
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Not calculated here.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Depends on wax, fragrance load, dye and jar shape. Found by burn testing.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wick size cannot be calculated. It depends on your wax, fragrance load, dye, and the diameter and shape of your vessel — the only way to know is to burn a test candle and watch the melt pool.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Use the burn test log that came with this sheet for that.</t>
-        </is>
-      </c>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The printable Burn Test Log supplied with this sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Starting assumptions</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Starting assumptions — all of them, and where to change them</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Starts at</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Change it on</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Starts at</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Why, and where to change it</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Wax factor</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Candle · wax is about 86% the density of water; waxes vary</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Water-to-wax factor</t>
+          <t>Pitcher loss</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wax is lighter than water — around 86% of its density. A planning assumption, not a constant. Waxes differ. Change it on Your Candle.</t>
+          <t>Candle · depends on your pitcher and pour</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Extra wax for the pitcher</t>
+          <t>Wholesale multiplier</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Starts at zero, because how much you lose depends on your pitcher and how you pour. Change it on Your Candle.</t>
+          <t>Costs &amp; Price</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wholesale multiplier</t>
+          <t>Selling fees</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>blank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A common starting point is twice what the candle costs you. Change it on Costs &amp; Price.</t>
+          <t>Costs &amp; Price · enter your own current rates</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Selling fees</t>
+          <t>Labour, overhead</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>off</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Left empty on purpose. Fees change, and they differ by marketplace and country. Look up yours and type them in on Costs &amp; Price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Your time and running costs</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>off</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Both optional. Switch them on when you want your price to cover them.</t>
+          <t>Costs &amp; Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Load and content</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fragrance as a % of the wax alone.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Fragrance load and fragrance content</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Fragrance as a % of wax + fragrance.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Fragrance load</t>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Example</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The fragrance as a percentage of the wax on its own.</t>
+          <t>20 g fragrance in 200 g wax = 10% load, 9.09% content.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Fragrance content</t>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Reference point</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The fragrance as a percentage of the wax and fragrance added together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>The worked example</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20 g of fragrance in 200 g of wax is a 10% load, and 9.09% content (20 out of 220 g). Same candle.</t>
+          <t>1 oz fragrance per 1 lb wax = 6.25% load.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>A handy reference point</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1 oz of fragrance per 1 lb of wax is a 6.25% load.</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Margin and markup</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Profit ÷ price.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Selling fees — what the boxes mean</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Markup</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Profit ÷ cost.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Selling fee %</t>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Watch out</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What the marketplace charges you for making the sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Payment processing %</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What the payment provider charges for taking the money.</t>
+          <t>Adding 40% to cost gives a 29% margin, not 40%.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Any other % fee</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Anything else charged as a percentage — advertising, for example.</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Fee boxes</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Fixed fee per order</t>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Selling fee</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>A flat amount per order rather than a percentage.</t>
+          <t>Marketplace commission.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Percentage fees apply to</t>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Processing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Some places charge their percentage on the item price plus the shipping you charge. Others only on the item price. Check yours.</t>
+          <t>Payment provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Other %</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Advertising or similar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Fixed per order</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Flat amount, not a percentage.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Margin and markup</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Margin</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Your profit as a share of the price you charge.</t>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Charged on</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Some charge on item + shipping, others item only.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Markup</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Your profit as a share of what the candle cost you.</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Cell colours</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Adding 40% to your cost does not give you a 40% margin. This sheet works out the price that actually gives you the margin you asked for, after fees.</t>
+          <t>Type here</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="n"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Assumption you can change</t>
         </is>
       </c>
     </row>

--- a/product/candle-calculator/dist/tests/T5a.xlsx
+++ b/product/candle-calculator/dist/tests/T5a.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>planning assumption — waxes vary</t>
+          <t>editable assumption — wax density varies by type</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1141,7 +1141,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="B32" s="19">
@@ -1478,12 +1478,12 @@
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>Not calculated here.</t>
+          <t>Not calculated</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Depends on wax, fragrance load, dye and jar shape. Found by burn testing.</t>
+          <t>Depends on wax, fragrance load, dye and jar shape. Confirmed by burn testing.</t>
         </is>
       </c>
     </row>
@@ -1495,14 +1495,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The printable Burn Test Log supplied with this sheet.</t>
+          <t>The printable Burn Test Log included with this download.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Starting assumptions</t>
+          <t>Editable assumptions</t>
         </is>
       </c>
       <c r="B7" s="4" t="n"/>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Starts at</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Candle · wax is about 86% the density of water; waxes vary</t>
+          <t>Candle · wax weighs about 86% of the same volume of water; varies by wax</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Candle · depends on your pitcher and pour</t>
+          <t>Candle · the wax left behind in your pouring pitcher</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Labour, overhead</t>
+          <t>Labor, overhead</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Costs &amp; Price</t>
+          <t>Costs &amp; Price · both are optional</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Watch out</t>
+          <t>Common error</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Fee boxes</t>
+          <t>Fee cells</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1784,7 +1784,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Cell colours</t>
+          <t>Cell colors</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1794,7 +1794,7 @@
       <c r="A34" s="2" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Type here</t>
+          <t>Enter your own numbers</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       <c r="A35" s="23" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>Calculated automatically</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       <c r="A36" s="24" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Assumption you can change</t>
+          <t>Editable assumption</t>
         </is>
       </c>
     </row>
